--- a/426-config---paramètre-pin-all/ig/StructureDefinition-tddui-encounter-sejour.xlsx
+++ b/426-config---paramètre-pin-all/ig/StructureDefinition-tddui-encounter-sejour.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T15:49:47+00:00</t>
+    <t>2026-01-30T16:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Encounter|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Encounter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -504,7 +504,7 @@
     <t>TDDUIAdmissionDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-admission-date|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-admission-date}
 </t>
   </si>
   <si>
@@ -523,7 +523,7 @@
     <t>TDDUIEntryModelabel</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-entry-mode-label|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-entry-mode-label}
 </t>
   </si>
   <si>
@@ -542,7 +542,7 @@
     <t>TDDUIExitModeLabel</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-exit-mode-label|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-exit-mode-label}
 </t>
   </si>
   <si>
@@ -561,7 +561,7 @@
     <t>TDDUIComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-comment}
 </t>
   </si>
   <si>
@@ -746,7 +746,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-encounter-identifier-vs</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -968,7 +968,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1073,7 +1073,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1092,7 +1092,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1614,7 +1614,7 @@
     <t>The reason for re-admission of this hospitalization encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0092|2.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0092</t>
   </si>
   <si>
     <t>PV1-13</t>
@@ -1823,7 +1823,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
 </t>
   </si>
   <si>
@@ -2178,7 +2178,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.68359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2193,7 +2193,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="64.00390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.91015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.40234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
